--- a/Captura de datos medidas cama/20240409 Ajustes de posición en impresora 3D.xlsx
+++ b/Captura de datos medidas cama/20240409 Ajustes de posición en impresora 3D.xlsx
@@ -66,9 +66,6 @@
     <t>Distancia que queda entre el borde de la cama cuando llega al dispositivo que la detecta atrás y la boquilla por delante que quedaría fuera de la cama (Y)</t>
   </si>
   <si>
-    <t>Distancia que recorre la boquilla desde el borde de la cama hasta que toca al sensor, microswitch, o dispositivo que detecta el final de carrera a la derecha (X)</t>
-  </si>
-  <si>
     <t>Distancia que recorre la boquilla desde el borde de la cama hasta que choca al final a la derecha (X)</t>
   </si>
   <si>
@@ -283,6 +280,9 @@
   </si>
   <si>
     <t># ni está, ni se pone en la máquina.</t>
+  </si>
+  <si>
+    <t>Distancia que recorre la boquilla desde el borde de la cama hasta que toca al sensor, microswitch, o dispositivo que detecta el final de carrera a la izquierda (X)</t>
   </si>
 </sst>
 </file>
@@ -412,39 +412,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>340179</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>145597</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>8582406</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>8508766</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="1 Imagen" descr="20230228 Medidas Cama impresora 3d.jpg"/>
+        <xdr:cNvPr id="3" name="2 Imagen" descr="20230228 Medidas Cama impresora 3d.png"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect l="9816"/>
+        <a:srcRect l="10629" b="5675"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="2486025"/>
-          <a:ext cx="7963281" cy="6381750"/>
+          <a:off x="340179" y="2717347"/>
+          <a:ext cx="8168587" cy="6521903"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="31750">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -766,44 +766,44 @@
     </row>
     <row r="2" spans="1:10" ht="13.5" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" thickBot="1">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="B3" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="13.5" thickBot="1">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.5" thickBot="1">
@@ -811,7 +811,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="9">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -822,13 +822,13 @@
         <v>15</v>
       </c>
       <c r="B6" s="9">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.5" thickBot="1">
@@ -836,24 +836,24 @@
         <v>0</v>
       </c>
       <c r="B7" s="9">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="10">
         <f>IF(B9&gt;0,B9+H31,H31)</f>
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J7" s="10">
         <f>IF(B10&gt;0,B10+H31,H31)</f>
-        <v>12</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.5" thickBot="1">
@@ -861,24 +861,24 @@
         <v>1</v>
       </c>
       <c r="B8" s="9">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8" s="10">
         <f>IF(B9&gt;0,B7-H31,B7-H31-(0-B9))</f>
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J8" s="10">
         <f>IF(B10&lt;0,B8-(0-B10)-H31,B8-H31)</f>
-        <v>208</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="13.5" thickBot="1">
@@ -886,17 +886,17 @@
         <v>2</v>
       </c>
       <c r="B9" s="9">
-        <v>-28</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="10">
         <f>0-B3</f>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.5" thickBot="1">
@@ -904,56 +904,56 @@
         <v>3</v>
       </c>
       <c r="B10" s="9">
-        <v>-15</v>
+        <v>35.5</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="10">
         <f>0-(B3+0.5)</f>
-        <v>-2.5</v>
+        <v>-6.5</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="D11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="10">
         <f>B7+B4</f>
-        <v>235.5</v>
+        <v>295</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" s="8"/>
       <c r="D12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="D15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -961,7 +961,7 @@
         <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="4:10">
@@ -969,10 +969,10 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="4:10">
@@ -980,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="4:10">
@@ -993,7 +993,7 @@
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="4:10">
@@ -1001,54 +1001,54 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H21" s="10">
         <f>B7/2</f>
-        <v>117.5</v>
+        <v>147.5</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="10">
         <f>B8/2</f>
-        <v>117.5</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="22" spans="4:10">
       <c r="D22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="10">
         <f>0-B6</f>
-        <v>-11.5</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="4:10">
       <c r="D23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="10">
         <f>0-(B6+0.5)</f>
-        <v>-12</v>
+        <v>-0.5</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="4:10">
       <c r="D24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="10">
         <f>B8+B5</f>
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="G24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="4:10">
@@ -1058,31 +1058,31 @@
     </row>
     <row r="28" spans="4:10">
       <c r="D28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="4:10">
       <c r="D29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="4:10">
       <c r="D30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="4:10">
       <c r="G31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H31" s="11">
         <v>12</v>
@@ -1090,85 +1090,85 @@
     </row>
     <row r="32" spans="4:10">
       <c r="D32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="4:7">
       <c r="D33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="4:7">
       <c r="D34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="4:7">
       <c r="D35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E35" s="10">
         <f>B9</f>
-        <v>-28</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="4:7">
       <c r="D36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E36" s="10">
         <f>B10</f>
-        <v>-15</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="37" spans="4:7">
       <c r="D37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="4:7">
       <c r="D39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="4:7">
       <c r="D40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="4:7">
       <c r="D41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E41" s="10">
         <f>B9</f>
-        <v>-28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="4:7">
       <c r="D42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E42" s="10">
         <f>B10</f>
-        <v>-15</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="43" spans="4:7">
       <c r="D43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1194,28 +1194,28 @@
   <sheetData>
     <row r="2" spans="1:8" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2">
         <v>-28.1</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75">
       <c r="A6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2">
         <v>-15</v>
@@ -1252,105 +1252,105 @@
     </row>
     <row r="7" spans="1:8" ht="15.75">
       <c r="A7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75">
       <c r="A11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75">
       <c r="A12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75">
       <c r="A14" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75">
       <c r="A16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75">
       <c r="A17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75">
       <c r="A18" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.75">
       <c r="A19" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.75">
       <c r="A20" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.75">
       <c r="A21" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.75">
       <c r="A22" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.75">
       <c r="A23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.75">
       <c r="A24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.75">
       <c r="A25" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.75">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
